--- a/outputs/build/diagnostics/excluded_standard_unit_obs.xlsx
+++ b/outputs/build/diagnostics/excluded_standard_unit_obs.xlsx
@@ -186,96 +186,96 @@
     <t>vendor_id</t>
   </si>
   <si>
+    <t>ANAOAQ31</t>
+  </si>
+  <si>
+    <t>KED6C3DL</t>
+  </si>
+  <si>
+    <t>AG60CRCP</t>
+  </si>
+  <si>
     <t>PTGS9CZB</t>
   </si>
   <si>
-    <t>ANAOAQ31</t>
-  </si>
-  <si>
-    <t>AG60CRCP</t>
-  </si>
-  <si>
-    <t>KED6C3DL</t>
+    <t>O6NGCL26</t>
   </si>
   <si>
     <t>S35CS7NJ</t>
   </si>
   <si>
-    <t>O6NGCL26</t>
-  </si>
-  <si>
     <t>HG2R8UR3</t>
   </si>
   <si>
     <t>GDTVNFV5</t>
   </si>
   <si>
+    <t>I8GEW5EU</t>
+  </si>
+  <si>
     <t>SXMR65WI</t>
   </si>
   <si>
-    <t>I8GEW5EU</t>
-  </si>
-  <si>
     <t>BF1CVWI7</t>
   </si>
   <si>
+    <t>UMOP0H16</t>
+  </si>
+  <si>
     <t>6IU6X8LE</t>
   </si>
   <si>
-    <t>UMOP0H16</t>
+    <t>81YD2D4Y</t>
   </si>
   <si>
     <t>7E61LTA6</t>
   </si>
   <si>
+    <t>3PQJGPX2</t>
+  </si>
+  <si>
     <t>K7QZ5BIX</t>
   </si>
   <si>
-    <t>3PQJGPX2</t>
-  </si>
-  <si>
     <t>UECM6ZZ7</t>
   </si>
   <si>
-    <t>81YD2D4Y</t>
-  </si>
-  <si>
     <t>REYDZ29A</t>
   </si>
   <si>
     <t>CUANELG7</t>
   </si>
   <si>
+    <t>XV2VXESL</t>
+  </si>
+  <si>
+    <t>3IJHQ24N</t>
+  </si>
+  <si>
     <t>MY7HILN0</t>
   </si>
   <si>
-    <t>3IJHQ24N</t>
-  </si>
-  <si>
-    <t>XV2VXESL</t>
-  </si>
-  <si>
     <t>P90EVCOR</t>
   </si>
   <si>
     <t>86YRLEXE</t>
   </si>
   <si>
+    <t>BHI84A67</t>
+  </si>
+  <si>
     <t>W3Y98A7M</t>
   </si>
   <si>
-    <t>BHI84A67</t>
+    <t>0X6CXPQB</t>
+  </si>
+  <si>
+    <t>B5LXNNSR</t>
   </si>
   <si>
     <t>6SML8FIT</t>
   </si>
   <si>
-    <t>0X6CXPQB</t>
-  </si>
-  <si>
-    <t>B5LXNNSR</t>
-  </si>
-  <si>
     <t>4JW4PL87</t>
   </si>
   <si>
@@ -297,24 +297,27 @@
     <t>DR4X8J9Z</t>
   </si>
   <si>
+    <t>8E5XGY1Y</t>
+  </si>
+  <si>
+    <t>2GQ9D2ZK</t>
+  </si>
+  <si>
     <t>EKKENYZA</t>
   </si>
   <si>
-    <t>8E5XGY1Y</t>
-  </si>
-  <si>
-    <t>2GQ9D2ZK</t>
+    <t>WAZ19DZ2</t>
+  </si>
+  <si>
+    <t>9B8ZS4PI</t>
+  </si>
+  <si>
+    <t>1RNST8HU</t>
   </si>
   <si>
     <t>SU9T7L6Y</t>
   </si>
   <si>
-    <t>WAZ19DZ2</t>
-  </si>
-  <si>
-    <t>1RNST8HU</t>
-  </si>
-  <si>
     <t>57T6R5X5</t>
   </si>
   <si>
@@ -324,24 +327,21 @@
     <t>U3E4WK7B</t>
   </si>
   <si>
-    <t>9B8ZS4PI</t>
-  </si>
-  <si>
     <t>XO779UU5</t>
   </si>
   <si>
+    <t>594IJ96W</t>
+  </si>
+  <si>
+    <t>FK0QULBI</t>
+  </si>
+  <si>
     <t>9ZZZITD0</t>
   </si>
   <si>
     <t>WGKFP079</t>
   </si>
   <si>
-    <t>594IJ96W</t>
-  </si>
-  <si>
-    <t>FK0QULBI</t>
-  </si>
-  <si>
     <t>JUGLALA7</t>
   </si>
   <si>
@@ -387,10 +387,10 @@
     <t>province_median</t>
   </si>
   <si>
+    <t>medium_size</t>
+  </si>
+  <si>
     <t>large_size</t>
-  </si>
-  <si>
-    <t>medium_size</t>
   </si>
   <si>
     <t>conventional_nsu</t>
@@ -491,7 +491,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1">
-        <v>6758</v>
+        <v>6756</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -522,7 +522,7 @@
         <v>113</v>
       </c>
       <c r="L2" s="1">
-        <v>235</v>
+        <v>285</v>
       </c>
       <c r="M2" t="s">
         <v>31</v>
@@ -536,7 +536,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1">
-        <v>6756</v>
+        <v>6757</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
@@ -567,7 +567,7 @@
         <v>113</v>
       </c>
       <c r="L3" s="1">
-        <v>285</v>
+        <v>330</v>
       </c>
       <c r="M3" t="s">
         <v>31</v>
@@ -626,7 +626,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1">
-        <v>6757</v>
+        <v>6758</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
@@ -657,7 +657,7 @@
         <v>113</v>
       </c>
       <c r="L5" s="1">
-        <v>330</v>
+        <v>235</v>
       </c>
       <c r="M5" t="s">
         <v>31</v>
@@ -671,7 +671,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1">
-        <v>6762</v>
+        <v>6761</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
@@ -692,7 +692,7 @@
         <v>52</v>
       </c>
       <c r="H6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="s">
         <v>61</v>
@@ -702,7 +702,7 @@
         <v>113</v>
       </c>
       <c r="L6" s="1">
-        <v>400</v>
+        <v>485</v>
       </c>
       <c r="M6" t="s">
         <v>32</v>
@@ -716,7 +716,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1">
-        <v>6761</v>
+        <v>6762</v>
       </c>
       <c r="B7" t="s">
         <v>2</v>
@@ -737,7 +737,7 @@
         <v>52</v>
       </c>
       <c r="H7" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="s">
         <v>62</v>
@@ -747,7 +747,7 @@
         <v>113</v>
       </c>
       <c r="L7" s="1">
-        <v>485</v>
+        <v>400</v>
       </c>
       <c r="M7" t="s">
         <v>32</v>
@@ -851,7 +851,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1">
-        <v>4044</v>
+        <v>4043</v>
       </c>
       <c r="B10" t="s">
         <v>3</v>
@@ -884,7 +884,7 @@
         <v>113</v>
       </c>
       <c r="L10" s="1">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="M10" t="s">
         <v>33</v>
@@ -898,7 +898,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1">
-        <v>4043</v>
+        <v>4044</v>
       </c>
       <c r="B11" t="s">
         <v>3</v>
@@ -931,7 +931,7 @@
         <v>113</v>
       </c>
       <c r="L11" s="1">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="M11" t="s">
         <v>33</v>
@@ -992,7 +992,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1">
-        <v>4632</v>
+        <v>4636</v>
       </c>
       <c r="B13" t="s">
         <v>3</v>
@@ -1013,7 +1013,7 @@
         <v>52</v>
       </c>
       <c r="H13" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" t="s">
         <v>68</v>
@@ -1023,7 +1023,7 @@
         <v>113</v>
       </c>
       <c r="L13" s="1">
-        <v>0.20000000298023224</v>
+        <v>220</v>
       </c>
       <c r="M13" t="s">
         <v>34</v>
@@ -1032,12 +1032,12 @@
         <v>34</v>
       </c>
       <c r="O13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1">
-        <v>4635</v>
+        <v>4633</v>
       </c>
       <c r="B14" t="s">
         <v>3</v>
@@ -1058,7 +1058,7 @@
         <v>52</v>
       </c>
       <c r="H14" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="s">
         <v>69</v>
@@ -1068,7 +1068,7 @@
         <v>113</v>
       </c>
       <c r="L14" s="1">
-        <v>170</v>
+        <v>0.2199999988079071</v>
       </c>
       <c r="M14" t="s">
         <v>34</v>
@@ -1077,12 +1077,12 @@
         <v>34</v>
       </c>
       <c r="O14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1">
-        <v>4637</v>
+        <v>4634</v>
       </c>
       <c r="B15" t="s">
         <v>3</v>
@@ -1103,7 +1103,7 @@
         <v>52</v>
       </c>
       <c r="H15" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" t="s">
         <v>69</v>
@@ -1113,7 +1113,7 @@
         <v>113</v>
       </c>
       <c r="L15" s="1">
-        <v>245</v>
+        <v>0.25999999046325684</v>
       </c>
       <c r="M15" t="s">
         <v>34</v>
@@ -1122,12 +1122,12 @@
         <v>34</v>
       </c>
       <c r="O15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1">
-        <v>4633</v>
+        <v>4632</v>
       </c>
       <c r="B16" t="s">
         <v>3</v>
@@ -1151,14 +1151,14 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" t="s">
         <v>113</v>
       </c>
       <c r="L16" s="1">
-        <v>0.2199999988079071</v>
+        <v>0.20000000298023224</v>
       </c>
       <c r="M16" t="s">
         <v>34</v>
@@ -1167,12 +1167,12 @@
         <v>34</v>
       </c>
       <c r="O16" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1">
-        <v>4634</v>
+        <v>4637</v>
       </c>
       <c r="B17" t="s">
         <v>3</v>
@@ -1193,7 +1193,7 @@
         <v>52</v>
       </c>
       <c r="H17" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" t="s">
         <v>68</v>
@@ -1203,7 +1203,7 @@
         <v>113</v>
       </c>
       <c r="L17" s="1">
-        <v>0.25999999046325684</v>
+        <v>245</v>
       </c>
       <c r="M17" t="s">
         <v>34</v>
@@ -1212,12 +1212,12 @@
         <v>34</v>
       </c>
       <c r="O17" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1">
-        <v>4636</v>
+        <v>4635</v>
       </c>
       <c r="B18" t="s">
         <v>3</v>
@@ -1241,14 +1241,14 @@
         <v>2</v>
       </c>
       <c r="I18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" t="s">
         <v>113</v>
       </c>
       <c r="L18" s="1">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="M18" t="s">
         <v>34</v>
@@ -1257,12 +1257,12 @@
         <v>34</v>
       </c>
       <c r="O18" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1">
-        <v>2329</v>
+        <v>2330</v>
       </c>
       <c r="B19" t="s">
         <v>4</v>
@@ -1283,7 +1283,7 @@
         <v>52</v>
       </c>
       <c r="H19" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I19" t="s">
         <v>70</v>
@@ -1302,12 +1302,12 @@
         <v>120</v>
       </c>
       <c r="O19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1">
-        <v>2331</v>
+        <v>2329</v>
       </c>
       <c r="B20" t="s">
         <v>4</v>
@@ -1347,7 +1347,7 @@
         <v>120</v>
       </c>
       <c r="O20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21">
@@ -1392,12 +1392,12 @@
         <v>120</v>
       </c>
       <c r="O21" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1">
-        <v>2332</v>
+        <v>2331</v>
       </c>
       <c r="B22" t="s">
         <v>4</v>
@@ -1437,12 +1437,12 @@
         <v>120</v>
       </c>
       <c r="O22" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1">
-        <v>2330</v>
+        <v>2332</v>
       </c>
       <c r="B23" t="s">
         <v>4</v>
@@ -1463,7 +1463,7 @@
         <v>52</v>
       </c>
       <c r="H23" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23" t="s">
         <v>74</v>
@@ -1482,7 +1482,7 @@
         <v>120</v>
       </c>
       <c r="O23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24">
@@ -1581,7 +1581,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1">
-        <v>5319</v>
+        <v>5321</v>
       </c>
       <c r="B26" t="s">
         <v>2</v>
@@ -1614,7 +1614,7 @@
         <v>113</v>
       </c>
       <c r="L26" s="1">
-        <v>0.27500000596046448</v>
+        <v>0.28499999642372131</v>
       </c>
       <c r="M26" t="s">
         <v>36</v>
@@ -1675,7 +1675,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1">
-        <v>5321</v>
+        <v>5319</v>
       </c>
       <c r="B28" t="s">
         <v>2</v>
@@ -1708,7 +1708,7 @@
         <v>113</v>
       </c>
       <c r="L28" s="1">
-        <v>0.28499999642372131</v>
+        <v>0.27500000596046448</v>
       </c>
       <c r="M28" t="s">
         <v>36</v>
@@ -1762,7 +1762,7 @@
         <v>120</v>
       </c>
       <c r="O29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30">
@@ -1807,12 +1807,12 @@
         <v>120</v>
       </c>
       <c r="O30" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B31" t="s">
         <v>5</v>
@@ -1833,7 +1833,7 @@
         <v>52</v>
       </c>
       <c r="H31" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I31" t="s">
         <v>82</v>
@@ -1852,12 +1852,12 @@
         <v>120</v>
       </c>
       <c r="O31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B32" t="s">
         <v>5</v>
@@ -1878,7 +1878,7 @@
         <v>52</v>
       </c>
       <c r="H32" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I32" t="s">
         <v>83</v>
@@ -1897,12 +1897,12 @@
         <v>120</v>
       </c>
       <c r="O32" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1">
-        <v>3878</v>
+        <v>3876</v>
       </c>
       <c r="B33" t="s">
         <v>3</v>
@@ -1923,7 +1923,7 @@
         <v>53</v>
       </c>
       <c r="H33" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I33" t="s">
         <v>84</v>
@@ -1949,7 +1949,7 @@
     </row>
     <row r="34">
       <c r="A34" s="1">
-        <v>3876</v>
+        <v>3879</v>
       </c>
       <c r="B34" t="s">
         <v>3</v>
@@ -1982,7 +1982,7 @@
         <v>113</v>
       </c>
       <c r="L34" s="1">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="M34" t="s">
         <v>38</v>
@@ -1996,7 +1996,7 @@
     </row>
     <row r="35">
       <c r="A35" s="1">
-        <v>3879</v>
+        <v>3878</v>
       </c>
       <c r="B35" t="s">
         <v>3</v>
@@ -2017,7 +2017,7 @@
         <v>53</v>
       </c>
       <c r="H35" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I35" t="s">
         <v>86</v>
@@ -2029,7 +2029,7 @@
         <v>113</v>
       </c>
       <c r="L35" s="1">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="M35" t="s">
         <v>38</v>
@@ -2130,7 +2130,7 @@
         <v>39</v>
       </c>
       <c r="O37" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38">
@@ -2175,7 +2175,7 @@
         <v>118</v>
       </c>
       <c r="O38" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="39">
@@ -2267,7 +2267,7 @@
         <v>42</v>
       </c>
       <c r="O40" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="41">
@@ -2362,7 +2362,7 @@
     </row>
     <row r="43">
       <c r="A43" s="1">
-        <v>2705</v>
+        <v>2704</v>
       </c>
       <c r="B43" t="s">
         <v>4</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="44">
       <c r="A44" s="1">
-        <v>2704</v>
+        <v>2703</v>
       </c>
       <c r="B44" t="s">
         <v>4</v>
@@ -2452,7 +2452,7 @@
     </row>
     <row r="45">
       <c r="A45" s="1">
-        <v>2703</v>
+        <v>2705</v>
       </c>
       <c r="B45" t="s">
         <v>4</v>
@@ -2497,7 +2497,7 @@
     </row>
     <row r="46">
       <c r="A46" s="1">
-        <v>10207</v>
+        <v>10210</v>
       </c>
       <c r="B46" t="s">
         <v>2</v>
@@ -2518,17 +2518,17 @@
         <v>52</v>
       </c>
       <c r="H46" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I46" t="s">
         <v>97</v>
       </c>
       <c r="J46" s="1"/>
       <c r="K46" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L46" s="1">
-        <v>21.670000076293945</v>
+        <v>6</v>
       </c>
       <c r="M46" t="s">
         <v>44</v>
@@ -2537,12 +2537,12 @@
         <v>44</v>
       </c>
       <c r="O46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1">
-        <v>10210</v>
+        <v>10206</v>
       </c>
       <c r="B47" t="s">
         <v>2</v>
@@ -2563,17 +2563,17 @@
         <v>52</v>
       </c>
       <c r="H47" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I47" t="s">
         <v>98</v>
       </c>
       <c r="J47" s="1"/>
       <c r="K47" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L47" s="1">
-        <v>6</v>
+        <v>21.004999160766602</v>
       </c>
       <c r="M47" t="s">
         <v>44</v>
@@ -2582,7 +2582,7 @@
         <v>44</v>
       </c>
       <c r="O47" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48">
@@ -2627,12 +2627,12 @@
         <v>44</v>
       </c>
       <c r="O48" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1">
-        <v>10205</v>
+        <v>10207</v>
       </c>
       <c r="B49" t="s">
         <v>2</v>
@@ -2653,17 +2653,17 @@
         <v>52</v>
       </c>
       <c r="H49" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I49" t="s">
         <v>100</v>
       </c>
       <c r="J49" s="1"/>
       <c r="K49" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L49" s="1">
-        <v>0.0060000000521540642</v>
+        <v>21.670000076293945</v>
       </c>
       <c r="M49" t="s">
         <v>44</v>
@@ -2672,12 +2672,12 @@
         <v>44</v>
       </c>
       <c r="O49" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1">
-        <v>10209</v>
+        <v>10205</v>
       </c>
       <c r="B50" t="s">
         <v>2</v>
@@ -2722,7 +2722,7 @@
     </row>
     <row r="51">
       <c r="A51" s="1">
-        <v>10208</v>
+        <v>10209</v>
       </c>
       <c r="B51" t="s">
         <v>2</v>
@@ -2743,7 +2743,7 @@
         <v>52</v>
       </c>
       <c r="H51" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I51" t="s">
         <v>102</v>
@@ -2753,7 +2753,7 @@
         <v>114</v>
       </c>
       <c r="L51" s="1">
-        <v>0.0065999999642372131</v>
+        <v>0.0060000000521540642</v>
       </c>
       <c r="M51" t="s">
         <v>44</v>
@@ -2762,12 +2762,12 @@
         <v>44</v>
       </c>
       <c r="O51" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1">
-        <v>10206</v>
+        <v>10208</v>
       </c>
       <c r="B52" t="s">
         <v>2</v>
@@ -2795,10 +2795,10 @@
       </c>
       <c r="J52" s="1"/>
       <c r="K52" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L52" s="1">
-        <v>21.004999160766602</v>
+        <v>0.0065999999642372131</v>
       </c>
       <c r="M52" t="s">
         <v>44</v>
@@ -2807,7 +2807,7 @@
         <v>44</v>
       </c>
       <c r="O52" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="53">
@@ -2852,12 +2852,12 @@
         <v>44</v>
       </c>
       <c r="O53" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1">
-        <v>10213</v>
+        <v>10212</v>
       </c>
       <c r="B54" t="s">
         <v>2</v>
@@ -2897,12 +2897,12 @@
         <v>45</v>
       </c>
       <c r="O54" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1">
-        <v>10215</v>
+        <v>10214</v>
       </c>
       <c r="B55" t="s">
         <v>2</v>
@@ -2923,7 +2923,7 @@
         <v>52</v>
       </c>
       <c r="H55" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I55" t="s">
         <v>106</v>
@@ -2942,12 +2942,12 @@
         <v>45</v>
       </c>
       <c r="O55" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1">
-        <v>10212</v>
+        <v>10213</v>
       </c>
       <c r="B56" t="s">
         <v>2</v>
@@ -2987,12 +2987,12 @@
         <v>45</v>
       </c>
       <c r="O56" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1">
-        <v>10214</v>
+        <v>10215</v>
       </c>
       <c r="B57" t="s">
         <v>2</v>
@@ -3013,7 +3013,7 @@
         <v>52</v>
       </c>
       <c r="H57" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I57" t="s">
         <v>108</v>
@@ -3032,7 +3032,7 @@
         <v>45</v>
       </c>
       <c r="O57" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="58">
